--- a/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
+++ b/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDE5F476-8EF4-4C9B-966E-BB7A60177DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685A760C-4D77-4D03-AEA1-AD8CABD67B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Etage</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>Nombre facade</t>
+  </si>
+  <si>
+    <t>Typologie</t>
+  </si>
+  <si>
+    <t>Vue</t>
   </si>
 </sst>
 </file>
@@ -439,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" customWidth="1"/>
@@ -465,9 +471,10 @@
     <col min="23" max="24" width="19" customWidth="1"/>
     <col min="25" max="27" width="17.90625" customWidth="1"/>
     <col min="28" max="28" width="32" customWidth="1"/>
+    <col min="29" max="29" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,6 +561,12 @@
       </c>
       <c r="AC1" s="1" t="s">
         <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
+++ b/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685A760C-4D77-4D03-AEA1-AD8CABD67B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20280334-7D5D-4572-8A56-3E0EB7E40E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>Nombre reception</t>
   </si>
   <si>
-    <t>Superficie totale</t>
-  </si>
-  <si>
     <t>Type bien</t>
   </si>
   <si>
@@ -113,6 +110,9 @@
   </si>
   <si>
     <t>Vue</t>
+  </si>
+  <si>
+    <t>Superficie vendable</t>
   </si>
 </sst>
 </file>
@@ -482,22 +482,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>3</v>
@@ -506,7 +506,7 @@
         <v>4</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>5</v>
@@ -539,34 +539,34 @@
         <v>14</v>
       </c>
       <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="AE1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
+++ b/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20280334-7D5D-4572-8A56-3E0EB7E40E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2D7D15-F0EA-4C77-832E-B25A5468D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>Etage</t>
   </si>
@@ -113,6 +113,18 @@
   </si>
   <si>
     <t>Superficie vendable</t>
+  </si>
+  <si>
+    <t>Orientation</t>
+  </si>
+  <si>
+    <t>Prix</t>
+  </si>
+  <si>
+    <t>Nombre Kitchenette</t>
+  </si>
+  <si>
+    <t>Nombre sejour</t>
   </si>
 </sst>
 </file>
@@ -445,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.90625" customWidth="1"/>
@@ -459,22 +471,23 @@
     <col min="10" max="10" width="12.81640625" customWidth="1"/>
     <col min="11" max="11" width="19" customWidth="1"/>
     <col min="12" max="12" width="19.1796875" customWidth="1"/>
-    <col min="13" max="13" width="17.54296875" customWidth="1"/>
-    <col min="14" max="14" width="16.1796875" customWidth="1"/>
-    <col min="15" max="15" width="14.1796875" customWidth="1"/>
-    <col min="16" max="16" width="12.08984375" customWidth="1"/>
-    <col min="17" max="17" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="18.54296875" customWidth="1"/>
-    <col min="20" max="20" width="19" customWidth="1"/>
-    <col min="21" max="22" width="17.90625" customWidth="1"/>
-    <col min="23" max="24" width="19" customWidth="1"/>
-    <col min="25" max="27" width="17.90625" customWidth="1"/>
-    <col min="28" max="28" width="32" customWidth="1"/>
-    <col min="29" max="29" width="15.08984375" customWidth="1"/>
+    <col min="13" max="15" width="17.54296875" customWidth="1"/>
+    <col min="16" max="16" width="16.1796875" customWidth="1"/>
+    <col min="17" max="17" width="14.1796875" customWidth="1"/>
+    <col min="18" max="18" width="12.08984375" customWidth="1"/>
+    <col min="19" max="19" width="15.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="18.54296875" customWidth="1"/>
+    <col min="22" max="22" width="19" customWidth="1"/>
+    <col min="23" max="24" width="17.90625" customWidth="1"/>
+    <col min="25" max="26" width="19" customWidth="1"/>
+    <col min="27" max="29" width="17.90625" customWidth="1"/>
+    <col min="30" max="30" width="32" customWidth="1"/>
+    <col min="31" max="31" width="15.08984375" customWidth="1"/>
+    <col min="33" max="33" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:35" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,58 +528,70 @@
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>29</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
+++ b/public/docs/exemplaires-import-biens/exemplaire_biens.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2D7D15-F0EA-4C77-832E-B25A5468D402}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77469A8-4F07-4F9B-91A1-5196304B5DB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50" yWindow="2280" windowWidth="19150" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -121,10 +121,10 @@
     <t>Prix</t>
   </si>
   <si>
-    <t>Nombre Kitchenette</t>
-  </si>
-  <si>
     <t>Nombre sejour</t>
+  </si>
+  <si>
+    <t>Nombre kitchenette</t>
   </si>
 </sst>
 </file>
@@ -528,10 +528,10 @@
         <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>7</v>
